--- a/EstablecimientoSalud/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
+++ b/EstablecimientoSalud/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>21225</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,22 +518,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-8.42314602</t>
+          <t>-8.40451046</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-78.78100527</t>
+          <t>-78.82199008</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>POLICLINICO VIRGEN DEL CARMEN</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIA VIRU</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AVENIDA AVENIDA VIRU 2130 PUENTE VIRU-VIRU DISTRITO VIRU PROVINCIA VIRU DEPARTAMENTO LA LIBERTAD</t>
+          <t>OTROS MZ N/LT 23/ SECTOR NUEVO VICTOR RAAL S/N VIRU VIRU LA LIBERTAD</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,12 +555,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21225</t>
+          <t>31087</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>131201</t>
+          <t>131202</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -575,27 +575,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VIRU</t>
+          <t>CHAO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-8.40451046</t>
+          <t>-8.53828162</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-78.82199008</t>
+          <t>-78.67883969</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIA VIRU</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO FORTALEZA DEL SOL CHAO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OTROS MZ N/LT 23/ SECTOR NUEVO VICTOR RAAL S/N VIRU VIRU LA LIBERTAD</t>
+          <t>CALLE SAN MARTIN 179 1 5 16 CHAO VIRU LA LIBERTAD</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,12 +617,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>31087</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>131202</t>
+          <t>131201</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -637,32 +637,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CHAO</t>
+          <t>VIRU</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-8.53828162</t>
+          <t>-8.4142357</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-78.67883969</t>
+          <t>-78.7527095</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO FORTALEZA DEL SOL CHAO</t>
+          <t>CENTRO DE SALUD "VICTOR SOLES GARCIA"</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CALLE SAN MARTIN 179 1 5 16 CHAO VIRU LA LIBERTAD</t>
+          <t>AVENIDA AVENIDA VICTOR RAUL S/N SECTOR SAN LUIS NUMERO S/N DISTRITO VIRU PROVINCIA VIRU DEPARTAMENTO LA LIBERTAD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -704,35 +704,531 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-8.4142357</t>
+          <t>-8.37955759</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-78.7527095</t>
+          <t>-78.67919934</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD "VICTOR SOLES GARCIA"</t>
+          <t>EL NINO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AVENIDA AVENIDA VICTOR RAUL S/N SECTOR SAN LUIS NUMERO S/N DISTRITO VIRU PROVINCIA VIRU DEPARTAMENTO LA LIBERTAD</t>
+          <t>OTROS EL NINO S/N NUMERO S/N DISTRITO VIRU PROVINCIA VIRU DEPARTAMENTO LA LIBERTAD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6827</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-8.40547544</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-78.82292712</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>VICTOR RAUL HAYA DE LA TORRE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>OTROS VICTOR RAUL PARTE BAJA MZ. 1 LOTE 2 VICTOR RAUL PARTE BAJA MZ. 1 LOTE 2 VIRU VIRU LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>I-3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5254</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-8.37444948</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-78.65343774</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>HUACAPONGO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>OTROS HUACAPONGO CENTRO DISTRITO VIRU PROVINCIA VIRU DEPARTAMENTO LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>9689</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-8.46761266</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-78.84787104</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>HUANCAQUITO BAJO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>OTROS BARRIO EL PROGRESO BARRIO EL PROGRESO VIRU VIRU LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5252</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-8.44758178</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-78.8181228</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>HUANCAQUITO ALTO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>OTROS HUANCAQUITO ALTO S/N S/N HUANCAQUITO ALTO S/N VIRU VIRU LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5253</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-8.40943349</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-78.8078677</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>OTROS CAKLLE TUPAC AMARU MZ. E LOTE 5 DISTRITO VIRU PROVINCIA VIRU DEPARTAMENTO LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>I-3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5257</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-8.4035853</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-78.89560614</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PUERTO MORIN</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>OTROS MZ.  12  LOTE 2 MZ.  12  LOTE 2 VIRU VIRU LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5255</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-8.46648318</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-78.86626848</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>EL CARMELO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>OTROS JOSE HERNANDEZ DE AGUERO S/N NUMERO S/N DISTRITO VIRU PROVINCIA VIRU DEPARTAMENTO LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>I-3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>16609</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-8.43229363</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-78.8308437</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SANTA ELENA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AVENIDA AV. VICTOR RAUL MZ.2 LOTE 6 AV. VICTOR RAUL MZ.2 LOTE 6 VIRU VIRU LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>131201</t>
         </is>

--- a/EstablecimientoSalud/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
+++ b/EstablecimientoSalud/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>21225</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>131201</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-8.40451046</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>131201</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>31087</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>131202</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CHAO</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-8.53828162</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>131201</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>11702</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>131201</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-8.4142357</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>131201</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>5256</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>131201</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-8.37955759</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>131201</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>6827</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>131201</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-8.40547544</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>131201</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>5254</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>131201</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-8.37444948</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>131201</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>9689</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>131201</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-8.46761266</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>131201</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>5252</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>131201</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-8.44758178</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>131201</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>5253</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>131201</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-8.40943349</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>131201</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>5257</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>131201</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-8.4035853</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>131201</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>5255</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>131201</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-8.46648318</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>131201</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>131201</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VIRU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>16609</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>131201</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>VIRU</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-8.43229363</t>
@@ -1226,11 +1166,6 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>131201</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
+++ b/EstablecimientoSalud/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/EstablecimientoSalud/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
+++ b/EstablecimientoSalud/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
